--- a/output/full_scan/batch_seq6_2026-08-31.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-31.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6214</v>
+        <v>6226</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>749.331536977062</v>
+        <v>938.7024278406188</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>183.5</v>
+        <v>31.6</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>75.53878335009028</v>
+        <v>69.31900818252191</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>36.61426635266138</v>
+        <v>29.78780965434271</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.477506895441635</v>
+        <v>3.00269890971602</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.8588417622295914</v>
+        <v>1.291011622149996</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>721.1815529688196</v>
+        <v>921.1815529688196</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>79.5</v>
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>61.67508360439678</v>
+        <v>61.67508360863916</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>14.05411744689161</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.256518206852501</v>
+        <v>1.256518206833426</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6224</v>
+        <v>6165</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>672.83708686572</v>
+        <v>907.1082939050652</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>65.74005120576687</v>
+        <v>61.86556579467314</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.39299036979938</v>
+        <v>11.37958699190014</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.415104879778758</v>
+        <v>2.512763336916208</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.640527795427268</v>
+        <v>0.1710637367653582</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>662.1071581696525</v>
+        <v>882.1071581696525</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>71.09999999999999</v>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>66.31309572856074</v>
+        <v>66.31309578890048</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.16955923511785</v>
+        <v>18.16955939690006</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>3.322016029739239</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.302268739287231</v>
+        <v>1.30226873905827</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6269</v>
+        <v>6187</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>647.3222747111525</v>
+        <v>871.6962819122069</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>1345</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>68.81665084160699</v>
+        <v>58.70791668592717</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.89009325084296</v>
+        <v>22.47006299690032</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.771661052742798</v>
+        <v>0.6812190789437909</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.310001074878818</v>
+        <v>11.09762364952719</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6165</v>
+        <v>6269</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>647.1082939050654</v>
+        <v>847.3222747111525</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>50.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.86556585996033</v>
+        <v>68.8166509199135</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11.37958694702328</v>
+        <v>20.89009331825376</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.512763336916208</v>
+        <v>4.771661052742798</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1710637364219319</v>
+        <v>1.310001074783429</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6416</v>
+        <v>6290</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>642.6922710980729</v>
+        <v>846.7560549759071</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>102</v>
+        <v>253.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.80536031199792</v>
+        <v>60.09805379597557</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.77289300073564</v>
+        <v>25.36788886689898</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5164857204166556</v>
+        <v>1.275605497590712</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1071557402485028</v>
+        <v>6.701620791504961</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6290</v>
+        <v>6426</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>636.7560549759071</v>
+        <v>813.8341193237001</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>253.5</v>
+        <v>261</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>60.09805378209933</v>
+        <v>65.76672933978013</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25.36788886472086</v>
+        <v>33.16182395308993</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.275605497590712</v>
+        <v>0.6354668887574162</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>6.701620791581282</v>
+        <v>3.1778056733231</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6226</v>
+        <v>6213</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>628.7024278406188</v>
+        <v>808.8406816929024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>31.6</v>
+        <v>548</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>69.31900818035125</v>
+        <v>65.83529415037069</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>29.7878095775755</v>
+        <v>30.91356426468552</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.00269890971602</v>
+        <v>0.9102233755044604</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.291011622176706</v>
+        <v>6.783294441193853</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6265</v>
+        <v>6173</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>619.1183119651948</v>
+        <v>790.8716451445689</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>57.4</v>
+        <v>246</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>53.34697413796782</v>
+        <v>62.25006593256513</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>22.59857999232993</v>
+        <v>19.46384180556135</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.3961625323097456</v>
+        <v>1.832590037714903</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.3200594827999312</v>
+        <v>6.313304171137524</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6213</v>
+        <v>6190</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>618.8406816929024</v>
+        <v>778.4470045711467</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>548</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>65.83529415491823</v>
+        <v>55.54478686744181</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>30.91356429216776</v>
+        <v>22.44694981218533</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9102233755044604</v>
+        <v>1.234089854913889</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>6.783294440487893</v>
+        <v>0.8989387992258173</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6426</v>
+        <v>6214</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>613.8341193237002</v>
+        <v>759.331536977062</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>261</v>
+        <v>183.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>65.76672933077809</v>
+        <v>75.53878337629057</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>33.16182393117536</v>
+        <v>36.61426636476846</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6354668887574162</v>
+        <v>0.477506895441635</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>3.177805673284979</v>
+        <v>0.8588417621341744</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>592.2212065253502</v>
+        <v>747.2212065253507</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>40.5</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.26052176988154</v>
+        <v>65.26052184207992</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>32.90885541239029</v>
+        <v>32.90885542759602</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.373791024265222</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.4149715273818548</v>
+        <v>0.4149715274295502</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6190</v>
+        <v>6416</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>568.4470045711453</v>
+        <v>717.6922710980729</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>102</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.54478688344963</v>
+        <v>56.80536035876097</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.44694976034366</v>
+        <v>14.77289307273549</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.234089854913889</v>
+        <v>0.5164857204166556</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.8989387993402971</v>
+        <v>0.1071557400386349</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6292</v>
+        <v>6418</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>556.8462769684432</v>
+        <v>715.7353981549475</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>62.2</v>
+        <v>34.35</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.7766560436755</v>
+        <v>55.01756601552571</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>26.44073525021954</v>
+        <v>26.78820342879693</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3103824185612894</v>
+        <v>2.173539815494746</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.1654401565733751</v>
+        <v>0.416322974414745</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6173</v>
+        <v>6278</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>550.8716451445689</v>
+        <v>696.8891394520333</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>246</v>
+        <v>199.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>62.25006593454143</v>
+        <v>62.08747988659509</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>19.46384186219288</v>
+        <v>20.61817114749109</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.832590037714903</v>
+        <v>0.5504852109047714</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>6.313304171003974</v>
+        <v>4.138398777186445</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6446</v>
+        <v>6225</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>548.7874528870841</v>
+        <v>693.6036495004231</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1395</v>
+        <v>60</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>51.24522289026346</v>
+        <v>67.81938145614164</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>35.59562994179498</v>
+        <v>51.92169536615724</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.343814275647959</v>
+        <v>0.670946533542869</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.6197199566793472</v>
+        <v>1.093737845570528</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6187</v>
+        <v>6224</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>546.6962819122077</v>
+        <v>692.83708686572</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1345</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.70791668232958</v>
+        <v>65.74005123046966</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.47006295012393</v>
+        <v>33.39299035004918</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6812190789437909</v>
+        <v>1.415104879778758</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>11.09762364905012</v>
+        <v>1.640527795284177</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6418</v>
+        <v>6265</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>535.7353981549475</v>
+        <v>659.1183119651948</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>34.35</v>
+        <v>57.4</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.01756602675101</v>
+        <v>53.34697414127057</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26.78820342380933</v>
+        <v>22.59858003304488</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.173539815494746</v>
+        <v>0.3961625323097456</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.4163229743956664</v>
+        <v>-0.3200594828132894</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6419</v>
+        <v>6272</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>535.2400529671312</v>
+        <v>613.1133243519893</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>154.5</v>
+        <v>26.15</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>52.49730801920742</v>
+        <v>57.26362975425899</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.4097401232851</v>
+        <v>40.98300669279108</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4051915119620418</v>
+        <v>5.182520660428114</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.142838512695564</v>
+        <v>0.5180862371351012</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6183</v>
+        <v>6197</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>524.5645426254014</v>
+        <v>611.710697940592</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>91</v>
+        <v>302.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>41.49795956351056</v>
+        <v>48.63974128519198</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>33.18189816603163</v>
+        <v>16.39981590704358</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.251271380757147</v>
+        <v>0.7248322289020747</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.3007448644359726</v>
+        <v>1.559779910068135</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6263</v>
+        <v>6449</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>517.4260500886835</v>
+        <v>605.7933872562004</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.35534125111091</v>
+        <v>47.5970239223622</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>13.09984929093319</v>
+        <v>22.87203074955331</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7012390565947472</v>
+        <v>1.222775403020954</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.4586120249633043</v>
+        <v>3.905846211435101</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6206</v>
+        <v>6275</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>503.9999334395852</v>
+        <v>604.3753446126431</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>138</v>
+        <v>46.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>48.95663460174802</v>
+        <v>57.30962778271317</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.25970920004992</v>
+        <v>22.23102608587266</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2196934372711223</v>
+        <v>1.426478653436415</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.246962911178851</v>
+        <v>0.3880514831001128</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6472</v>
+        <v>6168</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>502.3832029256002</v>
+        <v>599.1539909169146</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>433</v>
+        <v>28.45</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.48260411473767</v>
+        <v>61.4236732612362</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.77449653021263</v>
+        <v>18.96192731552077</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6090462498318142</v>
+        <v>0.6229306799885366</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.8132533718029098</v>
+        <v>0.5693118047243247</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6278</v>
+        <v>6271</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>491.8891394520331</v>
+        <v>597.9713955848634</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>199.5</v>
+        <v>212</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>62.08747988069122</v>
+        <v>58.08441499515024</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.61817108382552</v>
+        <v>14.17526453126604</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5504852109047714</v>
+        <v>0.9719137071519938</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>4.138398776804856</v>
+        <v>3.672874868154951</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6275</v>
+        <v>6292</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>489.3753446126432</v>
+        <v>596.8462769684432</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>46.3</v>
+        <v>62.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>57.30962768815422</v>
+        <v>55.77665606564526</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22.2310260265083</v>
+        <v>26.44073534581588</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.426478653436415</v>
+        <v>0.3103824185612894</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.3880514832336719</v>
+        <v>-0.1654401566878447</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6168</v>
+        <v>6442</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>484.1539909169146</v>
+        <v>580.0367240003892</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>28.45</v>
+        <v>1630</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>61.42367324212684</v>
+        <v>58.09693975276912</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18.96192725735434</v>
+        <v>19.85211429626632</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6229306799885366</v>
+        <v>1.18565076240017</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.569311804752944</v>
+        <v>16.66121997231145</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6277</v>
+        <v>6419</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>451.6091130575582</v>
+        <v>575.2400529671312</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>154.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46.13718092875384</v>
+        <v>52.49730801711164</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>34.70315324745506</v>
+        <v>22.4097401602901</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4252002414170466</v>
+        <v>0.4051915119620418</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.6697403908048087</v>
+        <v>-1.142838512542935</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6174</v>
+        <v>6257</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>449.9231702136517</v>
+        <v>572.5501015249506</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>45.25</v>
+        <v>208.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.44542431699882</v>
+        <v>51.01457063654696</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>12.61686846269984</v>
+        <v>13.11015838873964</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2759042233650786</v>
+        <v>2.129327140898645</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.4593530853226547</v>
+        <v>1.917611417380377</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6164</v>
+        <v>6465</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>447.6345940862941</v>
+        <v>565.5857805900272</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12.25</v>
+        <v>48.45</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.14245161588799</v>
+        <v>50.77174325649165</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.1493450591689</v>
+        <v>14.67990211020702</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5174106051425191</v>
+        <v>0.7426794909161566</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1150834564476095</v>
+        <v>0.5904455446807884</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6272</v>
+        <v>6241</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>443.1133243519894</v>
+        <v>563.7261341811356</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>26.15</v>
+        <v>17.05</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.26362948476167</v>
+        <v>57.36352651599155</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>40.98300666546386</v>
+        <v>23.3772467266439</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5.182520660428114</v>
+        <v>0.5063854591359203</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.5180862375548485</v>
+        <v>0.2350511151445647</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6449</v>
+        <v>6263</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>435.7933872562004</v>
+        <v>557.4260500886836</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>232</v>
+        <v>164</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>47.59702390493901</v>
+        <v>56.35534131497195</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.87203071552577</v>
+        <v>13.09984924846339</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.222775403020954</v>
+        <v>0.7012390565947472</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>3.905846211721282</v>
+        <v>0.4586120249633043</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6257</v>
+        <v>6456</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>432.5501015249505</v>
+        <v>553.9661866248055</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>208.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.01457059562785</v>
+        <v>56.87772443391598</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>13.11015804852862</v>
+        <v>16.15833851067952</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.129327140898645</v>
+        <v>1.254768153820134</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.917611418010002</v>
+        <v>0.8778556173447598</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>422.387328701857</v>
+        <v>548.9118960852854</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>77.5</v>
+        <v>1395</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>44.07392446729821</v>
+        <v>51.2452228930803</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>31.49744946520533</v>
+        <v>35.59563000689556</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.1289631040045618</v>
+        <v>2.379863734712477</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0908974157737632</v>
+        <v>0.619719955725401</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6423</v>
+        <v>6291</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>421.9353244688716</v>
+        <v>529.5939508094126</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>405</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>57.05897648772866</v>
+        <v>52.89887381496968</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.59633479921944</v>
+        <v>15.96648710995081</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2310987531272036</v>
+        <v>0.8287083877062406</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.2857605344430809</v>
+        <v>6.993693189679796</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6197</v>
+        <v>6183</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>421.7106979405923</v>
+        <v>524.5645426254014</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>302.5</v>
+        <v>91</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.63974125370312</v>
+        <v>41.49795955229629</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16.39981589588333</v>
+        <v>33.18189816603164</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.7248322289020747</v>
+        <v>1.251271380757147</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.559779909495727</v>
+        <v>-0.3007448644741289</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6271</v>
+        <v>6472</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>407.9713955848633</v>
+        <v>517.3832029256002</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>212</v>
+        <v>433</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.0844149672677</v>
+        <v>52.4826042576002</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.17526443755482</v>
+        <v>29.77449651855488</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9719137071519938</v>
+        <v>0.6090462498318142</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>3.672874868441125</v>
+        <v>0.8132533693225295</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6465</v>
+        <v>6206</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>385.5857805900272</v>
+        <v>503.9999334395852</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>48.45</v>
+        <v>138</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.77174312733296</v>
+        <v>48.95663476218875</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14.67990184784517</v>
+        <v>23.25970919131859</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7426794909161566</v>
+        <v>0.2196934372711223</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.5904455451876205</v>
+        <v>-1.246962911369658</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6442</v>
+        <v>6174</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>379.8832021201147</v>
+        <v>489.9231702136517</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1630</v>
+        <v>45.25</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.09693975390516</v>
+        <v>50.44542433649277</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19.85211429626632</v>
+        <v>12.61686844573177</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.173909406161029</v>
+        <v>0.2759042233650786</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>16.66121997173933</v>
+        <v>0.4593530853226547</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6462</v>
+        <v>6207</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>376.0317178392987</v>
+        <v>477.6405353445219</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>105.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.10813557123839</v>
+        <v>46.92727060539997</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>11.71751444919598</v>
+        <v>13.25601041165812</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5678744972255066</v>
+        <v>0.6986393732667781</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.589776760108649</v>
+        <v>1.453977971371168</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6456</v>
+        <v>6217</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>373.9661866248055</v>
+        <v>464.3368056701423</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>172.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>56.87772442173875</v>
+        <v>53.07374170207758</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.15833848354532</v>
+        <v>14.3018777462153</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.254768153820134</v>
+        <v>1.402710374290991</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.877855617440169</v>
+        <v>4.957668417286887</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>372.2961047389091</v>
+        <v>463.1586877277758</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>125.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.51768456124329</v>
+        <v>47.23349211342072</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15.36627058847112</v>
+        <v>15.8380521817765</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6031138819417429</v>
+        <v>1.276131133455254</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.3930436487225264</v>
+        <v>0.8679537631943801</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6474</v>
+        <v>6423</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>368.1432806764133</v>
+        <v>461.9353244688716</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>36.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>39.89881639326476</v>
+        <v>57.05897653459394</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.29642364471963</v>
+        <v>15.59633496670939</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8125279166028463</v>
+        <v>0.2310987531272036</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.2803171090940597</v>
+        <v>0.2857605340805631</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6243</v>
+        <v>6277</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>366.8826256468149</v>
+        <v>451.6091130575582</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>39.9</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>40.42717957155816</v>
+        <v>46.13718096181737</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.48205312810182</v>
+        <v>34.70315323429954</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2843423121766835</v>
+        <v>0.4252002414170466</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.5774592262195597</v>
+        <v>-0.6697403908620507</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6194</v>
+        <v>6164</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>365.3632422488132</v>
+        <v>437.6345940862941</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>29.8</v>
+        <v>12.25</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46.81941822085007</v>
+        <v>51.14245168695368</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>22.28314894847172</v>
+        <v>20.14934511323894</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.208118625872249</v>
+        <v>0.5174106051425191</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.09782965075181831</v>
+        <v>0.1150834564189897</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6175</v>
+        <v>6237</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>365.1546607847124</v>
+        <v>436.258734253196</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>73.5</v>
+        <v>34.65</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>41.45337313263363</v>
+        <v>47.78682067949367</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.39078582185457</v>
+        <v>21.04034449142044</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.8802140473086494</v>
+        <v>0.693957866710096</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.7460919098890488</v>
+        <v>0.4281041863859325</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6170</v>
+        <v>6464</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>358.5424999762595</v>
+        <v>422.387328701857</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>48.15</v>
+        <v>77.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>53.39475687172057</v>
+        <v>44.07392448499805</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21.8850452044889</v>
+        <v>31.49744953970513</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6609847289488653</v>
+        <v>0.1289631040045618</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.2465919656513241</v>
+        <v>-0.090897415811907</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6409</v>
+        <v>6191</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>357.0243481290811</v>
+        <v>417.367182369722</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1035</v>
+        <v>83.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>53.67422258487429</v>
+        <v>44.76773603053416</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.45085179231499</v>
+        <v>26.16274526188529</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6240884239870054</v>
+        <v>0.8027868393730594</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>2.631044274193318</v>
+        <v>0.4672981903171704</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6166</v>
+        <v>6438</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>356.9942279631961</v>
+        <v>417.0927482309842</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>115.5</v>
+        <v>148.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>39.45954662650467</v>
+        <v>53.31756211781273</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>16.64262908571227</v>
+        <v>13.25136909045922</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4874258488280995</v>
+        <v>0.9454492539443012</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.232814073173042</v>
+        <v>0.9158016215706708</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6261</v>
+        <v>6462</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>356.3714493403767</v>
+        <v>416.0317178392987</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>78</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>44.39656992814439</v>
+        <v>48.10813547345445</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.93822904669962</v>
+        <v>11.71751437949947</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7297717055300451</v>
+        <v>0.5678744972255066</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.6784282894158613</v>
+        <v>0.589776760108649</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6412</v>
+        <v>6177</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>353.6108045026965</v>
+        <v>413.3025079359099</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>79</v>
+        <v>47.1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46.85242882113186</v>
+        <v>45.82682731179503</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24.16665022339269</v>
+        <v>21.43793928906617</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8581518595589301</v>
+        <v>0.2910336186611209</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.4690014749566327</v>
+        <v>-0.1289412979241274</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6417</v>
+        <v>6279</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>352.435931135665</v>
+        <v>412.2961047389091</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>106</v>
+        <v>125.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>36.25788938084183</v>
+        <v>52.51768475310163</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>25.76327333996965</v>
+        <v>15.36627058847113</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5859218702442794</v>
+        <v>0.6031138819417429</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1299141108278698</v>
+        <v>-0.3930436491995204</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6477</v>
+        <v>6451</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>349.7737215717968</v>
+        <v>408.270289625488</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>36.45</v>
+        <v>456</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.38839102232223</v>
+        <v>53.3428971690778</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>19.56263352304192</v>
+        <v>10.01852831229891</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2577684383897334</v>
+        <v>0.8380276158113064</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0252208728540443</v>
+        <v>6.466288140543461</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6435</v>
+        <v>6474</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>348.7057457059933</v>
+        <v>408.1432806764133</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>244</v>
+        <v>36.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>40.54327195025741</v>
+        <v>39.8988166727205</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15.43003140883203</v>
+        <v>14.29642366334793</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9134354484439284</v>
+        <v>0.8125279166028463</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.694671603588425</v>
+        <v>-0.2803171093420913</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6202</v>
+        <v>6175</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>345.2425549805617</v>
+        <v>405.1546607847124</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>57.9</v>
+        <v>73.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.70324476362247</v>
+        <v>41.45337312702662</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.74195829833</v>
+        <v>18.39078586799545</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4291568589543718</v>
+        <v>0.8802140473086494</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0611680662100108</v>
+        <v>0.7460919098604424</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6177</v>
+        <v>6435</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>338.3025079359101</v>
+        <v>388.7057457059933</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>47.1</v>
+        <v>244</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45.82682721177</v>
+        <v>40.54327195313773</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.43793921103063</v>
+        <v>15.43003145544422</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2910336186611209</v>
+        <v>0.9134354484439284</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.1289412977333327</v>
+        <v>1.694671603588425</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6215</v>
+        <v>6270</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>338.1272942328504</v>
+        <v>376.069159477054</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>98</v>
+        <v>29.65</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.12191731250584</v>
+        <v>45.61471673807368</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.97155332048228</v>
+        <v>9.177112516600731</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3076749988872357</v>
+        <v>0.6357398510550588</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0050296968013432</v>
+        <v>0.1219270619877757</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6470</v>
+        <v>6230</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>336.0927990336791</v>
+        <v>370.8530984538239</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>41.5</v>
+        <v>108</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>30.03800419715256</v>
+        <v>44.09232860378264</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>44.05209079839651</v>
+        <v>15.546428172697</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.981887497796848</v>
+        <v>0.8801932433641412</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1693702589747618</v>
+        <v>0.6318003941798338</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6270</v>
+        <v>6243</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>336.069159477054</v>
+        <v>366.8826256468149</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>29.65</v>
+        <v>39.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.61471665779211</v>
+        <v>40.42717961766054</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>9.177112353055922</v>
+        <v>21.48205317069642</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6357398510550588</v>
+        <v>0.2843423121766835</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1219270620927103</v>
+        <v>-0.5774592264199002</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6414</v>
+        <v>6210</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>333.9143135697769</v>
+        <v>363.712662612178</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>389.5</v>
+        <v>18</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>41.54906523755469</v>
+        <v>51.40352455989339</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.75106132801432</v>
+        <v>6.539879980407837</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5911417985535395</v>
+        <v>0.9979705791302156</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-4.957919378492172</v>
+        <v>0.1314283165411092</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6284</v>
+        <v>6259</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>328.1586877277758</v>
+        <v>358.5876670907116</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.23349206223755</v>
+        <v>47.25023805568546</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15.83805210229156</v>
+        <v>11.00359075757392</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.276131133455254</v>
+        <v>0.6683279469693267</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.8679537634996435</v>
+        <v>0.1333633052054894</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6241</v>
+        <v>6170</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>323.7261341811357</v>
+        <v>358.5424999762596</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>17.05</v>
+        <v>48.15</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>57.36352645538001</v>
+        <v>53.39475711118654</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.37724666807731</v>
+        <v>21.88504528849448</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5063854591359203</v>
+        <v>0.6609847289488653</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.2350511152707185</v>
+        <v>0.2465919654986843</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6210</v>
+        <v>6234</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>323.712662612178</v>
+        <v>357.4678523276186</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>18</v>
+        <v>35.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>51.40352459281603</v>
+        <v>47.16139590773067</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6.539879888834377</v>
+        <v>18.6684604605293</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.9979705791302156</v>
+        <v>0.48667404604413</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1314283165029495</v>
+        <v>0.3515126378833311</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6246</v>
+        <v>6409</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>323.1478057013601</v>
+        <v>357.0243481290811</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>12.2</v>
+        <v>1035</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,49 +3891,49 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>41.04730300467997</v>
+        <v>53.67422262094937</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.79310549128694</v>
+        <v>19.45085182262824</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.133932744828323</v>
+        <v>0.6240884239870054</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0748669535258142</v>
+        <v>2.631044275147298</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6208</v>
+        <v>6166</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>322.420256875045</v>
+        <v>356.994227963196</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>81.7</v>
+        <v>115.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45.26163063189357</v>
+        <v>39.45954663547423</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>8.603311128880309</v>
+        <v>16.64262906736111</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4760838085398375</v>
+        <v>0.4874258488280995</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3405357275794474</v>
+        <v>-1.232814073115791</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6415</v>
+        <v>6261</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>321.6357923368548</v>
+        <v>356.3714493403767</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>412.5</v>
+        <v>78</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>38.47921736656008</v>
+        <v>44.39656994905085</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11.10298863451902</v>
+        <v>22.93822908631236</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.177541945733515</v>
+        <v>0.7297717055300451</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.274918954264759</v>
+        <v>0.6784282893967832</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6291</v>
+        <v>6412</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>319.5939508094125</v>
+        <v>353.6108045026965</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>405</v>
+        <v>79</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.89887381776129</v>
+        <v>46.85242924093199</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.96648710597561</v>
+        <v>24.1666502339457</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8287083877062406</v>
+        <v>0.8581518595589301</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>6.993693189717966</v>
+        <v>0.46900147323948</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6259</v>
+        <v>6285</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>318.5876670907116</v>
+        <v>353.4273042140797</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>30.4</v>
+        <v>244</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>47.25023806532734</v>
+        <v>50.67798128451889</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11.00359078063959</v>
+        <v>13.91621596798242</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6683279469693267</v>
+        <v>1.045897518213916</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1333633052054894</v>
+        <v>1.064829907006148</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6207</v>
+        <v>6477</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>317.6405353445219</v>
+        <v>349.7737215717968</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>105.5</v>
+        <v>36.45</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.9272705844572</v>
+        <v>49.3883910479268</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13.25601037356814</v>
+        <v>19.56263365549513</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6986393732667781</v>
+        <v>0.2577684383897334</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1.453977971457021</v>
+        <v>0.025220872758648</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6234</v>
+        <v>6215</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>317.4678523276187</v>
+        <v>348.1272942328504</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>35.8</v>
+        <v>98</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>47.16139585558764</v>
+        <v>47.12191742530205</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.66846043931129</v>
+        <v>11.97155337224633</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.48667404604413</v>
+        <v>0.3076749988872357</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.3515126379405654</v>
+        <v>0.0050296961526513</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6438</v>
+        <v>6202</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>312.0927482309842</v>
+        <v>345.2425549805617</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>148.5</v>
+        <v>57.9</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>53.31756211781273</v>
+        <v>47.7032448101037</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.25136906029866</v>
+        <v>12.74195830702634</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.9454492539443012</v>
+        <v>0.4291568589543718</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.9158016210936744</v>
+        <v>0.0611680660192244</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6191</v>
+        <v>6182</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>302.3671823697221</v>
+        <v>341.0516200994863</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>83.7</v>
+        <v>105.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.76773599387396</v>
+        <v>45.9763679611698</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>26.1627452706754</v>
+        <v>12.11524371693495</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8027868393730594</v>
+        <v>0.5036970709273474</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.4672981898211077</v>
+        <v>0.6293809318481176</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6182</v>
+        <v>6223</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>301.0516200994863</v>
+        <v>340.2134546091871</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>105.5</v>
+        <v>5130</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.97636795366776</v>
+        <v>40.94629269484236</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12.11524364310125</v>
+        <v>18.31087856262662</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5036970709273474</v>
+        <v>1.160297513632038</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.629380931895815</v>
+        <v>-78.15284340541587</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6223</v>
+        <v>6194</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>300.2134546091869</v>
+        <v>335.3632422488125</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>5130</v>
+        <v>29.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>40.94629268713918</v>
+        <v>46.81941848101288</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.31087850050177</v>
+        <v>22.28314897577987</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.160297513632038</v>
+        <v>0.208118625872249</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,11 +4439,11 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-78.15284340732299</v>
+        <v>0.09782965069458049</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>294.6218885094201</v>
+        <v>334.6218885094202</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>12.95</v>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>40.03829591866369</v>
+        <v>40.0382958389605</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25.53992954848093</v>
+        <v>25.539929623629</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>1.077636136754776</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0351230862377346</v>
+        <v>-0.0351230862186546</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4502,41 +4502,41 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6237</v>
+        <v>6288</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>281.2587342531959</v>
+        <v>333.9569523214448</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>34.65</v>
+        <v>20.95</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G77" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.7868205910369</v>
+        <v>57.2118022575267</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.04034444923925</v>
+        <v/>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.693957866710096</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.4281041864145414</v>
+        <v>-0.0141711397230861</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6441</v>
+        <v>6414</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>278.9854990363999</v>
+        <v>333.914313569777</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>21.25</v>
+        <v>389.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46.35393933994581</v>
+        <v>41.54906520146981</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.37631549908089</v>
+        <v>18.75106132879399</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.299413638315554</v>
+        <v>0.5911417985535395</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0534060373360268</v>
+        <v>-4.957919377538179</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6233</v>
+        <v>6417</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>276.0937289489643</v>
+        <v>332.435931135665</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>21.45</v>
+        <v>106</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.2271109572777</v>
+        <v>36.25788601984384</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.32765102339298</v>
+        <v>25.76327501646927</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.592446058328666</v>
+        <v>0.5859218702442794</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,51 +4651,51 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1484005637947767</v>
+        <v>0.1299141276368773</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6288</v>
+        <v>6235</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>274.0471752455182</v>
+        <v>330.6797589314965</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>20.95</v>
+        <v>38.95</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>44.27768280025433</v>
+        <v>50.79899022358273</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v/>
+        <v>11.18522431989482</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>0.6020530627292765</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0001777997045697</v>
+        <v>0.1802417967788531</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6411</v>
+        <v>6208</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>272.9534291970087</v>
+        <v>322.420256875045</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>79.8</v>
+        <v>81.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.26108569650109</v>
+        <v>45.26163057424139</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.91899531179581</v>
+        <v>8.603311072081969</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6457933045536799</v>
+        <v>0.4760838085398375</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.759527962611741</v>
+        <v>0.3405357277416181</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6405</v>
+        <v>6415</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>272.4960879001457</v>
+        <v>321.6357923368548</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>39</v>
+        <v>412.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.1174114887592</v>
+        <v>38.47921739207136</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>22.99418595476036</v>
+        <v>11.1029886586146</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5108187591776964</v>
+        <v>1.177541945733515</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.7106176215564348</v>
+        <v>1.274918953692369</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6220</v>
+        <v>6443</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>271.7545355363025</v>
+        <v>317.1531344037618</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>25.95</v>
+        <v>26</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.91872254487131</v>
+        <v>42.55039810761269</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>20.98420475517234</v>
+        <v>13.05233939924099</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4132479244269659</v>
+        <v>0.9353560177183028</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.3026630899178131</v>
+        <v>0.2406505733711488</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6239</v>
+        <v>6233</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>271.5461015977794</v>
+        <v>316.0937289489643</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>277</v>
+        <v>21.45</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.07310950456407</v>
+        <v>47.22711101371926</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.69372934906664</v>
+        <v>14.32765106458035</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9374632455748132</v>
+        <v>1.592446058328666</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>2.648149805432726</v>
+        <v>0.1484005637470774</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6229</v>
+        <v>6411</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>263.6241186195438</v>
+        <v>312.9534291970087</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>23.95</v>
+        <v>79.8</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.45949596744311</v>
+        <v>49.26108573817486</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.30694237072264</v>
+        <v>13.91899531869642</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3504350995915392</v>
+        <v>0.6457933045536799</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.1051853245755572</v>
+        <v>0.7595279625544915</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6176</v>
+        <v>6220</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>261.8015351575571</v>
+        <v>311.7545355363025</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>91.2</v>
+        <v>25.95</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.55167384633154</v>
+        <v>42.91872253132226</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>27.64160865499316</v>
+        <v>20.98420475744228</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5083465524751192</v>
+        <v>0.4132479244269659</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>1.100434102946242</v>
+        <v>0.3026630899178131</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6230</v>
+        <v>6470</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>260.8530984538239</v>
+        <v>306.0927990336791</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>108</v>
+        <v>41.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.09232853905553</v>
+        <v>30.03800444206922</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.54642812732692</v>
+        <v>44.05209081486218</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8801932433641412</v>
+        <v>0.981887497796848</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.6318003944660298</v>
+        <v>0.169370258955676</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6163</v>
+        <v>6229</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>257.3803896238945</v>
+        <v>303.6241186195438</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>42</v>
+        <v>23.95</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>47.4561548277811</v>
+        <v>50.45949599221535</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.19573264479564</v>
+        <v>13.30694237342771</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3866884955766856</v>
+        <v>0.3504350995915392</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1979711784042277</v>
+        <v>0.1051853245087794</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6227</v>
+        <v>6163</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>256.5587676260797</v>
+        <v>297.3803896238944</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.72714002818121</v>
+        <v>47.45615485245891</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10.38445670322559</v>
+        <v>16.19573263491606</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.191364243443953</v>
+        <v>0.3866884955766856</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-1.055752283108803</v>
+        <v>0.1979711783660727</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6196</v>
+        <v>6227</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>255.6134835657251</v>
+        <v>296.5587676260801</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>485</v>
+        <v>111</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.94651606072355</v>
+        <v>40.72714007960411</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>11.17667457977551</v>
+        <v>10.38445675380523</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6322342686265831</v>
+        <v>1.191364243443953</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.021762636757872</v>
+        <v>-1.055752283318662</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5244,21 +5244,21 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6274</v>
+        <v>6246</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>247.1335760558211</v>
+        <v>293.1478057013601</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1435</v>
+        <v>12.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.98545029524229</v>
+        <v>41.04730305512636</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.47172916276282</v>
+        <v>20.79310553518206</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.278426998724164</v>
+        <v>0.133932744828323</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-10.37126664057776</v>
+        <v>0.0748669534971968</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6443</v>
+        <v>6274</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>242.1531344037618</v>
+        <v>287.1335760558212</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>26</v>
+        <v>1435</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.55039809793205</v>
+        <v>47.9854502944516</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13.05233935681808</v>
+        <v>13.47172914964444</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.9353560177183028</v>
+        <v>1.278426998724164</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,11 +5340,11 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.2406505734474664</v>
+        <v>-10.37126663847905</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>242.0717533293331</v>
+        <v>282.0717533293331</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>24.05</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.21755450899489</v>
+        <v>45.21755450488553</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.03020734611299</v>
+        <v>16.03020738507131</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.5995192664313652</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.012374508615204</v>
+        <v>0.0123745085579647</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6222</v>
+        <v>6204</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>239.9703874229168</v>
+        <v>279.7666944162708</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>19.9</v>
+        <v>84</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>51.12839575027609</v>
+        <v>50.88933082999449</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>8.580691722015672</v>
+        <v>18.27034124118418</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.537564563743958</v>
+        <v>0.7751453715866494</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.3697540521082973</v>
+        <v>1.112152259606563</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6204</v>
+        <v>6432</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>239.7666944162707</v>
+        <v>273.5314921748133</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>84</v>
+        <v>62.6</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>50.88933077915013</v>
+        <v>39.32506465801377</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18.27034118653107</v>
+        <v>13.23957902347379</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7751453715866494</v>
+        <v>0.4721304260491586</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>1.112152260178958</v>
+        <v>-0.6986666515081899</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6184</v>
+        <v>6405</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>238.7206609289935</v>
+        <v>272.4960879001457</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>40.95</v>
+        <v>39</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>19.41780166540693</v>
+        <v>43.11741151152687</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>26.42792166843708</v>
+        <v>22.99418588442059</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.420301898551888</v>
+        <v>0.5108187591776964</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0264987354350723</v>
+        <v>0.7106176215373607</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6432</v>
+        <v>6245</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>233.5314921748133</v>
+        <v>266.6160552639698</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>62.6</v>
+        <v>81.8</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>39.32506466776011</v>
+        <v>48.08337573642834</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.23957891478861</v>
+        <v>10.82038622078308</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4721304260491586</v>
+        <v>1.336243660811485</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.6986666515558848</v>
+        <v>-0.2186772356296405</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6245</v>
+        <v>6176</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>226.6160552639696</v>
+        <v>261.8015351575571</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>81.8</v>
+        <v>91.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.08337565218002</v>
+        <v>52.55167409833424</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>10.82038608410823</v>
+        <v>27.64160867306447</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.336243660811485</v>
+        <v>0.5083465524751192</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.2186772354197582</v>
+        <v>1.100434101311302</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6283</v>
+        <v>6239</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>225.8239933636888</v>
+        <v>256.5461015977794</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>19.8</v>
+        <v>277</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>38.12310618755032</v>
+        <v>50.07310951318969</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>29.55419576929389</v>
+        <v>11.69372937024278</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.29453862976316</v>
+        <v>0.9374632455748132</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0797227991870888</v>
+        <v>2.648149805623563</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6217</v>
+        <v>6196</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>224.3368056701423</v>
+        <v>255.6134835657237</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>172.5</v>
+        <v>485</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,49 +5746,49 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>53.07374169573612</v>
+        <v>43.94651607638561</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.30187773499152</v>
+        <v>11.17667461725354</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.402710374290991</v>
+        <v>0.6322342686265831</v>
       </c>
       <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M100" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>4.957668417305956</v>
+        <v>-0.021762637234806</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6285</v>
+        <v>6441</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>223.4273042140797</v>
+        <v>248.9854990363998</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>244</v>
+        <v>21.25</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>50.67798128843088</v>
+        <v>46.35393958055752</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13.9162159281991</v>
+        <v>19.37631574803468</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.045897518213916</v>
+        <v>0.299413638315554</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>1.064829906910763</v>
+        <v>-0.0534060377366941</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6236</v>
+        <v>6184</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>221.8972878329431</v>
+        <v>238.7206609289936</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0</v>
+        <v>40.95</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>47.2661279169273</v>
+        <v>19.41780153963617</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>9.378742744373939</v>
+        <v>26.42792166325902</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0</v>
+        <v>1.420301898551888</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3238860743438339</v>
+        <v>-0.0264987353969126</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6451</v>
+        <v>6283</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>218.2702896254879</v>
+        <v>225.8239933636888</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>456</v>
+        <v>19.8</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>53.34289715655092</v>
+        <v>38.12310646117984</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.01852819865842</v>
+        <v>29.55419591181892</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.8380276158113064</v>
+        <v>1.29453862976316</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>6.46628814111585</v>
+        <v>0.0797227990439931</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6235</v>
+        <v>6236</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>215.6797589314965</v>
+        <v>221.8972878329431</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>38.95</v>
+        <v>0</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.79899017563637</v>
+        <v>47.2661279169273</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11.18522426445546</v>
+        <v>9.378742516279637</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6020530627292765</v>
+        <v>0</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1802417968742563</v>
+        <v>-0.3238860743438339</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6198</v>
+        <v>6266</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>210.1567812487124</v>
+        <v>217.2786346109408</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0</v>
+        <v>24.85</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>34.77994861855132</v>
+        <v>46.03014019733742</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>7.518891095148401</v>
+        <v>11.75352662248312</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.0003495070362121</v>
+        <v>0.6985873339117236</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.140070067110955</v>
+        <v>0.0266315046945545</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6167</v>
+        <v>6198</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>204.1675344675986</v>
+        <v>210.1567812487124</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.44340460896462</v>
+        <v>34.77994861539524</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.66523631111398</v>
+        <v>7.518891095294084</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2.2786408732064</v>
+        <v>0.0003495070362121</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0570144703752126</v>
+        <v>-1.140070067110955</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6201</v>
+        <v>6222</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>200.1142953607069</v>
+        <v>209.9703874229168</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>44.55</v>
+        <v>19.9</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>31.99844514413394</v>
+        <v>51.12839576709854</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>26.02283627319732</v>
+        <v>8.580691978792228</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.188799475837539</v>
+        <v>0.537564563743958</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,11 +6135,11 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.052181619298117</v>
+        <v>0.3697540519842819</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>197.7439323445792</v>
+        <v>207.7439323445792</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>44.9</v>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.62727333338347</v>
+        <v>42.62727336707718</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.29420479968855</v>
+        <v>16.29420491422152</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.5329839643609739</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1652405601639917</v>
+        <v>0.1652405601067526</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6266</v>
+        <v>6201</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>197.2786346109408</v>
+        <v>200.1142953607073</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>24.85</v>
+        <v>44.55</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.03014016899214</v>
+        <v>31.99844519113988</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.75352661699028</v>
+        <v>26.02283625026149</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6985873339117236</v>
+        <v>1.188799475837539</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0266315047517944</v>
+        <v>0.0521816193171995</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6276</v>
+        <v>6167</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>195.2633450138021</v>
+        <v>174.1675344675986</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>20.1</v>
+        <v>10.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>48.35882344780687</v>
+        <v>44.44340474956986</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>21.56168162716767</v>
+        <v>13.66523632707163</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.626366999242298</v>
+        <v>2.2786408732064</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2065822641606812</v>
+        <v>0.057014470342513</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6203</v>
+        <v>6228</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>183.6704285742043</v>
+        <v>167.8706386274316</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>59.8</v>
+        <v>0</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>33.17606134082929</v>
+        <v>39.24634457458146</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.34538341291335</v>
+        <v>8.875314290556004</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.762536282468237</v>
+        <v>0.002523340903356</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1499734573588886</v>
+        <v>-1.224189765519515</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6216</v>
+        <v>6276</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>150.3604180631004</v>
+        <v>165.2633450138021</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>20.65</v>
+        <v>20.1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>28.48796339889149</v>
+        <v>48.35882358676825</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17.28348989993207</v>
+        <v>21.56168158469616</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.283662743611393</v>
+        <v>0.626366999242298</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1586481541156399</v>
+        <v>0.2065822641416005</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6192</v>
+        <v>6203</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>143.9402114064956</v>
+        <v>153.6704285742044</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>116.5</v>
+        <v>59.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.0234655010273</v>
+        <v>33.17606157846757</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.78629482775453</v>
+        <v>17.34538341553038</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.253582005156171</v>
+        <v>0.762536282468237</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.148333247015015</v>
+        <v>0.1499734572825721</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6189</v>
+        <v>6216</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>138.4190320696055</v>
+        <v>150.3604180631004</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>48.1</v>
+        <v>20.65</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.68634273718392</v>
+        <v>28.48796340513829</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.978878802009425</v>
+        <v>17.28348993912979</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.807399998469277</v>
+        <v>1.283662743611393</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0439967042088411</v>
+        <v>-0.158648154125179</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6228</v>
+        <v>6188</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>127.8706386274315</v>
+        <v>147.1574246865429</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0</v>
+        <v>67.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.24634457736374</v>
+        <v>38.75769763326154</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.875314242582323</v>
+        <v>18.53609571883395</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.002523340903356</v>
+        <v>1.222625563505113</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-1.224189765538593</v>
+        <v>0.0576692222811627</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>127.1574246865402</v>
+        <v>143.9402114064958</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>67.2</v>
+        <v>116.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.75769753611125</v>
+        <v>50.0234655131964</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>18.53609573067349</v>
+        <v>16.78629486492555</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.222625563505113</v>
+        <v>1.253582005156171</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0576692223956436</v>
+        <v>0.1483332468623864</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,52 +6622,105 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
+        <v>6189</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>138.4190320696055</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>46.68634258983407</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>7.978878926477491</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.807399998469277</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.0439967042851592</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>6281</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>全國電</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>124.2174209157375</v>
-      </c>
-      <c r="E117" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>124.2174209157372</v>
+      </c>
+      <c r="E118" s="2" t="n">
         <v>51.3</v>
       </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>45.3761794119614</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>12.85014889489295</v>
-      </c>
-      <c r="J117" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>45.37617961534153</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>12.85014884102477</v>
+      </c>
+      <c r="J118" s="2" t="n">
         <v>0.944188733196896</v>
       </c>
-      <c r="K117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>-0.0248928040733399</v>
-      </c>
-      <c r="O117" s="2" t="inlineStr">
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-0.024892804168744</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
